--- a/exports/trend_1d/MARICO_full_report.xlsx
+++ b/exports/trend_1d/MARICO_full_report.xlsx
@@ -18,9 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,10 +53,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q59"/>
+  <dimension ref="A1:U59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,6 +512,26 @@
           <t>candles_held</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>expiry</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>reached_expiry</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>rule_trades</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>rule_wins</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -534,19 +557,19 @@
         <v>10.02</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>42129</v>
+        <v>42130</v>
       </c>
       <c r="H2" t="n">
-        <v>193</v>
+        <v>187.55</v>
       </c>
       <c r="I2" t="n">
         <v>187.9346469496284</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="K2" t="n">
-        <v>8.609999999999999</v>
+        <v>5.54</v>
       </c>
       <c r="L2" t="n">
         <v>4.71</v>
@@ -564,7 +587,19 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>72</v>
+        <v>73</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>42033</v>
+      </c>
+      <c r="S2" t="b">
+        <v>1</v>
+      </c>
+      <c r="T2" t="n">
+        <v>5</v>
+      </c>
+      <c r="U2" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="3">
@@ -591,19 +626,19 @@
         <v>15.13</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>42146</v>
+        <v>42149</v>
       </c>
       <c r="H3" t="n">
-        <v>205.13</v>
+        <v>208.78</v>
       </c>
       <c r="I3" t="n">
         <v>208.659897914018</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="K3" t="n">
-        <v>-9.369999999999999</v>
+        <v>-11.32</v>
       </c>
       <c r="L3" t="n">
         <v>12.5</v>
@@ -621,7 +656,19 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>42152</v>
+      </c>
+      <c r="S3" t="b">
+        <v>0</v>
+      </c>
+      <c r="T3" t="n">
+        <v>1</v>
+      </c>
+      <c r="U3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -648,28 +695,28 @@
         <v>11.42</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>42237</v>
+        <v>42240</v>
       </c>
       <c r="H4" t="n">
-        <v>215.3</v>
+        <v>198.13</v>
       </c>
       <c r="I4" t="n">
         <v>203.7834041322402</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="K4" t="n">
-        <v>3.12</v>
+        <v>-5.1</v>
       </c>
       <c r="L4" t="n">
-        <v>4.16</v>
+        <v>8.52</v>
       </c>
       <c r="M4" t="n">
         <v>3.38</v>
       </c>
       <c r="N4" t="n">
-        <v>5.34</v>
+        <v>7.97</v>
       </c>
       <c r="O4" t="n">
         <v>1.78</v>
@@ -678,7 +725,19 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>65</v>
+        <v>66</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>42152</v>
+      </c>
+      <c r="S4" t="b">
+        <v>1</v>
+      </c>
+      <c r="T4" t="n">
+        <v>4</v>
+      </c>
+      <c r="U4" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="5">
@@ -705,28 +764,28 @@
         <v>13.13</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>42325</v>
+        <v>42326</v>
       </c>
       <c r="H5" t="n">
-        <v>200.98</v>
+        <v>209.48</v>
       </c>
       <c r="I5" t="n">
         <v>205.2671333247119</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="K5" t="n">
-        <v>-1.44</v>
+        <v>-5.73</v>
       </c>
       <c r="L5" t="n">
-        <v>6.6</v>
+        <v>7.23</v>
       </c>
       <c r="M5" t="n">
         <v>1.92</v>
       </c>
       <c r="N5" t="n">
-        <v>2.92</v>
+        <v>4.23</v>
       </c>
       <c r="O5" t="n">
         <v>-7.97</v>
@@ -735,7 +794,19 @@
         <v>1</v>
       </c>
       <c r="Q5" t="n">
-        <v>57</v>
+        <v>58</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>42243</v>
+      </c>
+      <c r="S5" t="b">
+        <v>1</v>
+      </c>
+      <c r="T5" t="n">
+        <v>4</v>
+      </c>
+      <c r="U5" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="6">
@@ -762,19 +833,19 @@
         <v>10.28</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>42636</v>
+        <v>42639</v>
       </c>
       <c r="H6" t="n">
-        <v>284.45</v>
+        <v>278.5</v>
       </c>
       <c r="I6" t="n">
         <v>278.6009693252975</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="K6" t="n">
-        <v>35.79</v>
+        <v>32.95</v>
       </c>
       <c r="L6" t="n">
         <v>4.05</v>
@@ -792,7 +863,19 @@
         <v>1</v>
       </c>
       <c r="Q6" t="n">
-        <v>210</v>
+        <v>211</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>42334</v>
+      </c>
+      <c r="S6" t="b">
+        <v>1</v>
+      </c>
+      <c r="T6" t="n">
+        <v>11</v>
+      </c>
+      <c r="U6" t="n">
+        <v>10</v>
       </c>
     </row>
     <row r="7">
@@ -819,19 +902,19 @@
         <v>7.67</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>42745</v>
+        <v>42746</v>
       </c>
       <c r="H7" t="n">
-        <v>260.75</v>
+        <v>261</v>
       </c>
       <c r="I7" t="n">
         <v>260.8136852437271</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="K7" t="n">
-        <v>6.37</v>
+        <v>6.28</v>
       </c>
       <c r="L7" t="n">
         <v>4.09</v>
@@ -849,7 +932,19 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>73</v>
+        <v>74</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>42642</v>
+      </c>
+      <c r="S7" t="b">
+        <v>1</v>
+      </c>
+      <c r="T7" t="n">
+        <v>5</v>
+      </c>
+      <c r="U7" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="8">
@@ -876,19 +971,19 @@
         <v>6.29</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>43004</v>
+        <v>43005</v>
       </c>
       <c r="H8" t="n">
-        <v>316.6</v>
+        <v>314.35</v>
       </c>
       <c r="I8" t="n">
         <v>316.0513655251824</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="K8" t="n">
-        <v>21.3</v>
+        <v>20.44</v>
       </c>
       <c r="L8" t="n">
         <v>3.24</v>
@@ -906,7 +1001,19 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>176</v>
+        <v>177</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>42760</v>
+      </c>
+      <c r="S8" t="b">
+        <v>1</v>
+      </c>
+      <c r="T8" t="n">
+        <v>9</v>
+      </c>
+      <c r="U8" t="n">
+        <v>8</v>
       </c>
     </row>
     <row r="9">
@@ -933,19 +1040,19 @@
         <v>7.15</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>43077</v>
+        <v>43080</v>
       </c>
       <c r="H9" t="n">
-        <v>311.95</v>
+        <v>313.05</v>
       </c>
       <c r="I9" t="n">
         <v>312.925836926338</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="K9" t="n">
-        <v>0.76</v>
+        <v>0.41</v>
       </c>
       <c r="L9" t="n">
         <v>3.04</v>
@@ -963,7 +1070,19 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>50</v>
+        <v>51</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>43006</v>
+      </c>
+      <c r="S9" t="b">
+        <v>1</v>
+      </c>
+      <c r="T9" t="n">
+        <v>4</v>
+      </c>
+      <c r="U9" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="10">
@@ -990,28 +1109,28 @@
         <v>5.32</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>43132</v>
+        <v>43133</v>
       </c>
       <c r="H10" t="n">
-        <v>310.7</v>
+        <v>304.5</v>
       </c>
       <c r="I10" t="n">
         <v>304.9437097882114</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.75</v>
+        <v>-2.73</v>
       </c>
       <c r="L10" t="n">
         <v>6.39</v>
       </c>
       <c r="M10" t="n">
-        <v>0.53</v>
+        <v>0.84</v>
       </c>
       <c r="N10" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="O10" t="n">
         <v>0.35</v>
@@ -1020,7 +1139,19 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>37</v>
+        <v>38</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>43097</v>
+      </c>
+      <c r="S10" t="b">
+        <v>1</v>
+      </c>
+      <c r="T10" t="n">
+        <v>3</v>
+      </c>
+      <c r="U10" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="11">
@@ -1047,28 +1178,28 @@
         <v>8.119999999999999</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>43178</v>
+        <v>43179</v>
       </c>
       <c r="H11" t="n">
-        <v>303.25</v>
+        <v>318.95</v>
       </c>
       <c r="I11" t="n">
         <v>317.632774799732</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="K11" t="n">
-        <v>0.41</v>
+        <v>-4.75</v>
       </c>
       <c r="L11" t="n">
-        <v>4.76</v>
+        <v>5.01</v>
       </c>
       <c r="M11" t="n">
         <v>3.2</v>
       </c>
       <c r="N11" t="n">
-        <v>4.32</v>
+        <v>5.18</v>
       </c>
       <c r="O11" t="n">
         <v>-2</v>
@@ -1077,7 +1208,19 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>43153</v>
+      </c>
+      <c r="S11" t="b">
+        <v>1</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -1104,19 +1247,19 @@
         <v>9.789999999999999</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>43347</v>
+        <v>43348</v>
       </c>
       <c r="H12" t="n">
-        <v>354.5</v>
+        <v>352.05</v>
       </c>
       <c r="I12" t="n">
         <v>353.1794017748983</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="K12" t="n">
-        <v>11.15</v>
+        <v>10.38</v>
       </c>
       <c r="L12" t="n">
         <v>5.31</v>
@@ -1134,7 +1277,19 @@
         <v>1</v>
       </c>
       <c r="Q12" t="n">
-        <v>116</v>
+        <v>117</v>
+      </c>
+      <c r="R12" s="3" t="n">
+        <v>43187</v>
+      </c>
+      <c r="S12" t="b">
+        <v>1</v>
+      </c>
+      <c r="T12" t="n">
+        <v>7</v>
+      </c>
+      <c r="U12" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="13">
@@ -1161,19 +1316,19 @@
         <v>8.51</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>43405</v>
+        <v>43406</v>
       </c>
       <c r="H13" t="n">
-        <v>320</v>
+        <v>338.05</v>
       </c>
       <c r="I13" t="n">
         <v>333.597950342609</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="K13" t="n">
-        <v>9.1</v>
+        <v>3.98</v>
       </c>
       <c r="L13" t="n">
         <v>2.61</v>
@@ -1182,7 +1337,7 @@
         <v>1.21</v>
       </c>
       <c r="N13" t="n">
-        <v>3.06</v>
+        <v>5.64</v>
       </c>
       <c r="O13" t="n">
         <v>-0.6899999999999999</v>
@@ -1191,7 +1346,19 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>38</v>
+        <v>39</v>
+      </c>
+      <c r="R13" s="3" t="n">
+        <v>43370</v>
+      </c>
+      <c r="S13" t="b">
+        <v>1</v>
+      </c>
+      <c r="T13" t="n">
+        <v>3</v>
+      </c>
+      <c r="U13" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="14">
@@ -1218,19 +1385,19 @@
         <v>12.39</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>43508</v>
+        <v>43509</v>
       </c>
       <c r="H14" t="n">
-        <v>358.15</v>
+        <v>347.2</v>
       </c>
       <c r="I14" t="n">
         <v>357.8616161011045</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="K14" t="n">
-        <v>5.95</v>
+        <v>2.71</v>
       </c>
       <c r="L14" t="n">
         <v>4.78</v>
@@ -1248,7 +1415,19 @@
         <v>1</v>
       </c>
       <c r="Q14" t="n">
-        <v>69</v>
+        <v>70</v>
+      </c>
+      <c r="R14" s="3" t="n">
+        <v>43433</v>
+      </c>
+      <c r="S14" t="b">
+        <v>1</v>
+      </c>
+      <c r="T14" t="n">
+        <v>4</v>
+      </c>
+      <c r="U14" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="15">
@@ -1275,22 +1454,22 @@
         <v>9.73</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>43566</v>
+        <v>43567</v>
       </c>
       <c r="H15" t="n">
-        <v>358.45</v>
+        <v>360.1</v>
       </c>
       <c r="I15" t="n">
         <v>359.5397224394484</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="K15" t="n">
-        <v>-3.24</v>
+        <v>-3.72</v>
       </c>
       <c r="L15" t="n">
-        <v>4.41</v>
+        <v>4.84</v>
       </c>
       <c r="M15" t="n">
         <v>3.91</v>
@@ -1305,7 +1484,19 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>40</v>
+        <v>41</v>
+      </c>
+      <c r="R15" s="3" t="n">
+        <v>43524</v>
+      </c>
+      <c r="S15" t="b">
+        <v>1</v>
+      </c>
+      <c r="T15" t="n">
+        <v>3</v>
+      </c>
+      <c r="U15" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="16">
@@ -1332,28 +1523,28 @@
         <v>6.03</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>43588</v>
+        <v>43591</v>
       </c>
       <c r="H16" t="n">
-        <v>356.05</v>
+        <v>339.6</v>
       </c>
       <c r="I16" t="n">
         <v>343.6622871745071</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="K16" t="n">
-        <v>-1.12</v>
+        <v>-5.69</v>
       </c>
       <c r="L16" t="n">
-        <v>2.68</v>
+        <v>6.26</v>
       </c>
       <c r="M16" t="n">
         <v>0.48</v>
       </c>
       <c r="N16" t="n">
-        <v>1.78</v>
+        <v>4.62</v>
       </c>
       <c r="O16" t="n">
         <v>0.46</v>
@@ -1362,7 +1553,19 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R16" s="3" t="n">
+        <v>43580</v>
+      </c>
+      <c r="S16" t="b">
+        <v>1</v>
+      </c>
+      <c r="T16" t="n">
+        <v>2</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="17">
@@ -1389,22 +1592,22 @@
         <v>9.83</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>43616</v>
+        <v>43619</v>
       </c>
       <c r="H17" t="n">
-        <v>371.95</v>
+        <v>377.45</v>
       </c>
       <c r="I17" t="n">
         <v>372.9721610100235</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="K17" t="n">
-        <v>-9.529999999999999</v>
+        <v>-11.15</v>
       </c>
       <c r="L17" t="n">
-        <v>10.42</v>
+        <v>11.78</v>
       </c>
       <c r="M17" t="n">
         <v>3.56</v>
@@ -1419,7 +1622,19 @@
         <v>1</v>
       </c>
       <c r="Q17" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R17" s="3" t="n">
+        <v>43615</v>
+      </c>
+      <c r="S17" t="b">
+        <v>1</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="18">
@@ -1446,25 +1661,25 @@
         <v>6.75</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>43669</v>
+        <v>43670</v>
       </c>
       <c r="H18" t="n">
-        <v>361.25</v>
+        <v>360.3</v>
       </c>
       <c r="I18" t="n">
         <v>360.9336014347929</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="K18" t="n">
-        <v>-4.29</v>
+        <v>-4.54</v>
       </c>
       <c r="L18" t="n">
-        <v>5.05</v>
+        <v>5.99</v>
       </c>
       <c r="M18" t="n">
-        <v>0.44</v>
+        <v>0.5</v>
       </c>
       <c r="N18" t="n">
         <v>2.12</v>
@@ -1476,7 +1691,19 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>36</v>
+        <v>37</v>
+      </c>
+      <c r="R18" s="3" t="n">
+        <v>43643</v>
+      </c>
+      <c r="S18" t="b">
+        <v>1</v>
+      </c>
+      <c r="T18" t="n">
+        <v>2</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="19">
@@ -1503,22 +1730,22 @@
         <v>4.81</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>43682</v>
+        <v>43683</v>
       </c>
       <c r="H19" t="n">
-        <v>373.6</v>
+        <v>377.7</v>
       </c>
       <c r="I19" t="n">
         <v>377.6234367787043</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K19" t="n">
-        <v>-3.69</v>
+        <v>-4.83</v>
       </c>
       <c r="L19" t="n">
-        <v>4.58</v>
+        <v>6.36</v>
       </c>
       <c r="M19" t="n">
         <v>0.61</v>
@@ -1533,7 +1760,19 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R19" s="3" t="n">
+        <v>43671</v>
+      </c>
+      <c r="S19" t="b">
+        <v>1</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="20">
@@ -1560,28 +1799,28 @@
         <v>6.92</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>43765</v>
+        <v>43767</v>
       </c>
       <c r="H20" t="n">
-        <v>391.1</v>
+        <v>366.6</v>
       </c>
       <c r="I20" t="n">
         <v>373.1205052566532</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="K20" t="n">
-        <v>3.55</v>
+        <v>-2.94</v>
       </c>
       <c r="L20" t="n">
-        <v>2.3</v>
+        <v>4.09</v>
       </c>
       <c r="M20" t="n">
         <v>0.99</v>
       </c>
       <c r="N20" t="n">
-        <v>2.95</v>
+        <v>6.26</v>
       </c>
       <c r="O20" t="n">
         <v>1.1</v>
@@ -1590,7 +1829,19 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>53</v>
+        <v>54</v>
+      </c>
+      <c r="R20" s="3" t="n">
+        <v>43706</v>
+      </c>
+      <c r="S20" t="b">
+        <v>1</v>
+      </c>
+      <c r="T20" t="n">
+        <v>3</v>
+      </c>
+      <c r="U20" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="21">
@@ -1617,19 +1868,19 @@
         <v>11.52</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>43928</v>
+        <v>43929</v>
       </c>
       <c r="H21" t="n">
-        <v>283.85</v>
+        <v>289.45</v>
       </c>
       <c r="I21" t="n">
         <v>289.1803027229344</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="K21" t="n">
-        <v>22.57</v>
+        <v>21.04</v>
       </c>
       <c r="L21" t="n">
         <v>6.14</v>
@@ -1647,7 +1898,19 @@
         <v>1</v>
       </c>
       <c r="Q21" t="n">
-        <v>111</v>
+        <v>112</v>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>43769</v>
+      </c>
+      <c r="S21" t="b">
+        <v>1</v>
+      </c>
+      <c r="T21" t="n">
+        <v>7</v>
+      </c>
+      <c r="U21" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="22">
@@ -1674,19 +1937,19 @@
         <v>19.6</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>44092</v>
+        <v>44095</v>
       </c>
       <c r="H22" t="n">
-        <v>362.5</v>
+        <v>350.3</v>
       </c>
       <c r="I22" t="n">
         <v>354.2120645413525</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="K22" t="n">
-        <v>25.24</v>
+        <v>21.02</v>
       </c>
       <c r="L22" t="n">
         <v>4.27</v>
@@ -1695,7 +1958,7 @@
         <v>3.98</v>
       </c>
       <c r="N22" t="n">
-        <v>3.25</v>
+        <v>3.37</v>
       </c>
       <c r="O22" t="n">
         <v>1.97</v>
@@ -1704,7 +1967,19 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>114</v>
+        <v>115</v>
+      </c>
+      <c r="R22" s="3" t="n">
+        <v>43951</v>
+      </c>
+      <c r="S22" t="b">
+        <v>1</v>
+      </c>
+      <c r="T22" t="n">
+        <v>6</v>
+      </c>
+      <c r="U22" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="23">
@@ -1731,28 +2006,28 @@
         <v>8.369999999999999</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>44105</v>
+        <v>44109</v>
       </c>
       <c r="H23" t="n">
-        <v>361.9</v>
+        <v>376.9</v>
       </c>
       <c r="I23" t="n">
         <v>366.4866644594138</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="K23" t="n">
-        <v>-3.31</v>
+        <v>-7.59</v>
       </c>
       <c r="L23" t="n">
-        <v>4.58</v>
+        <v>8.26</v>
       </c>
       <c r="M23" t="n">
         <v>0.7</v>
       </c>
       <c r="N23" t="n">
-        <v>3.18</v>
+        <v>4.14</v>
       </c>
       <c r="O23" t="n">
         <v>-3.37</v>
@@ -1761,7 +2036,19 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R23" s="3" t="n">
+        <v>44098</v>
+      </c>
+      <c r="S23" t="b">
+        <v>1</v>
+      </c>
+      <c r="T23" t="n">
+        <v>2</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="24">
@@ -1788,19 +2075,19 @@
         <v>9.99</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>44252</v>
+        <v>44253</v>
       </c>
       <c r="H24" t="n">
-        <v>409.8</v>
+        <v>397.55</v>
       </c>
       <c r="I24" t="n">
         <v>400.2483971247154</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="K24" t="n">
-        <v>8.73</v>
+        <v>5.48</v>
       </c>
       <c r="L24" t="n">
         <v>8.26</v>
@@ -1818,7 +2105,19 @@
         <v>1</v>
       </c>
       <c r="Q24" t="n">
-        <v>101</v>
+        <v>102</v>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>44133</v>
+      </c>
+      <c r="S24" t="b">
+        <v>1</v>
+      </c>
+      <c r="T24" t="n">
+        <v>6</v>
+      </c>
+      <c r="U24" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="25">
@@ -1845,19 +2144,19 @@
         <v>10.35</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>44293</v>
+        <v>44294</v>
       </c>
       <c r="H25" t="n">
-        <v>408</v>
+        <v>414.65</v>
       </c>
       <c r="I25" t="n">
         <v>413.9289444173535</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="K25" t="n">
-        <v>-2.63</v>
+        <v>-4.3</v>
       </c>
       <c r="L25" t="n">
         <v>4.89</v>
@@ -1875,7 +2174,19 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R25" s="3" t="n">
+        <v>44280</v>
+      </c>
+      <c r="S25" t="b">
+        <v>1</v>
+      </c>
+      <c r="T25" t="n">
+        <v>2</v>
+      </c>
+      <c r="U25" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="26">
@@ -1902,19 +2213,19 @@
         <v>7.12</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>44517</v>
+        <v>44518</v>
       </c>
       <c r="H26" t="n">
-        <v>551.75</v>
+        <v>541.8</v>
       </c>
       <c r="I26" t="n">
         <v>546.6222098520562</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="K26" t="n">
-        <v>33.06</v>
+        <v>30.66</v>
       </c>
       <c r="L26" t="n">
         <v>3.12</v>
@@ -1932,7 +2243,19 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>152</v>
+        <v>153</v>
+      </c>
+      <c r="R26" s="3" t="n">
+        <v>44315</v>
+      </c>
+      <c r="S26" t="b">
+        <v>1</v>
+      </c>
+      <c r="T26" t="n">
+        <v>8</v>
+      </c>
+      <c r="U26" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="27">
@@ -1959,19 +2282,19 @@
         <v>7.35</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>44592</v>
+        <v>44593</v>
       </c>
       <c r="H27" t="n">
-        <v>482.55</v>
+        <v>497.65</v>
       </c>
       <c r="I27" t="n">
         <v>494.9790048077675</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="K27" t="n">
-        <v>10.94</v>
+        <v>8.15</v>
       </c>
       <c r="L27" t="n">
         <v>2.25</v>
@@ -1980,7 +2303,7 @@
         <v>1.59</v>
       </c>
       <c r="N27" t="n">
-        <v>2.34</v>
+        <v>3.13</v>
       </c>
       <c r="O27" t="n">
         <v>-1.8</v>
@@ -1989,7 +2312,19 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>51</v>
+        <v>52</v>
+      </c>
+      <c r="R27" s="3" t="n">
+        <v>44525</v>
+      </c>
+      <c r="S27" t="b">
+        <v>1</v>
+      </c>
+      <c r="T27" t="n">
+        <v>4</v>
+      </c>
+      <c r="U27" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="28">
@@ -2016,19 +2351,19 @@
         <v>8.6</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>44642</v>
+        <v>44643</v>
       </c>
       <c r="H28" t="n">
-        <v>492.1</v>
+        <v>484.6</v>
       </c>
       <c r="I28" t="n">
         <v>487.2655661956329</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="K28" t="n">
-        <v>-1.12</v>
+        <v>-2.62</v>
       </c>
       <c r="L28" t="n">
         <v>4.17</v>
@@ -2046,7 +2381,19 @@
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>34</v>
+        <v>35</v>
+      </c>
+      <c r="R28" s="3" t="n">
+        <v>44616</v>
+      </c>
+      <c r="S28" t="b">
+        <v>1</v>
+      </c>
+      <c r="T28" t="n">
+        <v>2</v>
+      </c>
+      <c r="U28" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="29">
@@ -2073,28 +2420,28 @@
         <v>9.710000000000001</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>44651</v>
+        <v>44652</v>
       </c>
       <c r="H29" t="n">
-        <v>503.7</v>
+        <v>518.25</v>
       </c>
       <c r="I29" t="n">
         <v>513.7838289854267</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K29" t="n">
-        <v>-3.94</v>
+        <v>-6.94</v>
       </c>
       <c r="L29" t="n">
-        <v>4.46</v>
+        <v>7.45</v>
       </c>
       <c r="M29" t="n">
         <v>0.98</v>
       </c>
       <c r="N29" t="n">
-        <v>2.8</v>
+        <v>2.89</v>
       </c>
       <c r="O29" t="n">
         <v>-1.52</v>
@@ -2103,7 +2450,19 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="R29" s="3" t="n">
+        <v>44651</v>
+      </c>
+      <c r="S29" t="b">
+        <v>1</v>
+      </c>
+      <c r="T29" t="n">
+        <v>2</v>
+      </c>
+      <c r="U29" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="30">
@@ -2130,22 +2489,22 @@
         <v>8.550000000000001</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>44687</v>
+        <v>44690</v>
       </c>
       <c r="H30" t="n">
-        <v>503.65</v>
+        <v>489.45</v>
       </c>
       <c r="I30" t="n">
         <v>496.7437742901559</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="K30" t="n">
-        <v>-2.82</v>
+        <v>-5.56</v>
       </c>
       <c r="L30" t="n">
-        <v>3.71</v>
+        <v>6.02</v>
       </c>
       <c r="M30" t="n">
         <v>3.47</v>
@@ -2160,7 +2519,19 @@
         <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R30" s="3" t="n">
+        <v>44679</v>
+      </c>
+      <c r="S30" t="b">
+        <v>1</v>
+      </c>
+      <c r="T30" t="n">
+        <v>2</v>
+      </c>
+      <c r="U30" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="31">
@@ -2187,19 +2558,19 @@
         <v>10.91</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>44762</v>
+        <v>44763</v>
       </c>
       <c r="H31" t="n">
-        <v>513.15</v>
+        <v>525.8</v>
       </c>
       <c r="I31" t="n">
         <v>516.5548678527763</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="K31" t="n">
-        <v>-4.84</v>
+        <v>-7.43</v>
       </c>
       <c r="L31" t="n">
         <v>12.76</v>
@@ -2217,7 +2588,19 @@
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>53</v>
+        <v>54</v>
+      </c>
+      <c r="R31" s="3" t="n">
+        <v>44707</v>
+      </c>
+      <c r="S31" t="b">
+        <v>1</v>
+      </c>
+      <c r="T31" t="n">
+        <v>3</v>
+      </c>
+      <c r="U31" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="32">
@@ -2244,22 +2627,22 @@
         <v>7.47</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>44844</v>
+        <v>44845</v>
       </c>
       <c r="H32" t="n">
-        <v>514.85</v>
+        <v>506.85</v>
       </c>
       <c r="I32" t="n">
         <v>508.0183200675141</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="K32" t="n">
-        <v>-2.08</v>
+        <v>-3.6</v>
       </c>
       <c r="L32" t="n">
-        <v>4.1</v>
+        <v>4.51</v>
       </c>
       <c r="M32" t="n">
         <v>1.98</v>
@@ -2274,7 +2657,19 @@
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>54</v>
+        <v>55</v>
+      </c>
+      <c r="R32" s="3" t="n">
+        <v>44770</v>
+      </c>
+      <c r="S32" t="b">
+        <v>1</v>
+      </c>
+      <c r="T32" t="n">
+        <v>4</v>
+      </c>
+      <c r="U32" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="33">
@@ -2301,19 +2696,19 @@
         <v>9.41</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>44903</v>
+        <v>44904</v>
       </c>
       <c r="H33" t="n">
-        <v>510.5</v>
+        <v>523.75</v>
       </c>
       <c r="I33" t="n">
         <v>513.4955875679275</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="K33" t="n">
-        <v>-0.72</v>
+        <v>-3.33</v>
       </c>
       <c r="L33" t="n">
         <v>6.93</v>
@@ -2331,7 +2726,19 @@
         <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>41</v>
+        <v>42</v>
+      </c>
+      <c r="R33" s="3" t="n">
+        <v>44861</v>
+      </c>
+      <c r="S33" t="b">
+        <v>1</v>
+      </c>
+      <c r="T33" t="n">
+        <v>3</v>
+      </c>
+      <c r="U33" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="34">
@@ -2358,19 +2765,19 @@
         <v>6.55</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>44938</v>
+        <v>44939</v>
       </c>
       <c r="H34" t="n">
-        <v>501.6</v>
+        <v>496.55</v>
       </c>
       <c r="I34" t="n">
         <v>499.7725204160971</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="K34" t="n">
-        <v>-4.23</v>
+        <v>-5.19</v>
       </c>
       <c r="L34" t="n">
         <v>6.37</v>
@@ -2388,7 +2795,19 @@
         <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R34" s="3" t="n">
+        <v>44924</v>
+      </c>
+      <c r="S34" t="b">
+        <v>1</v>
+      </c>
+      <c r="T34" t="n">
+        <v>2</v>
+      </c>
+      <c r="U34" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="35">
@@ -2415,19 +2834,19 @@
         <v>7.27</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>45041</v>
+        <v>45042</v>
       </c>
       <c r="H35" t="n">
-        <v>489.75</v>
+        <v>496.95</v>
       </c>
       <c r="I35" t="n">
         <v>490.3963809226809</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="K35" t="n">
-        <v>1.37</v>
+        <v>-0.08</v>
       </c>
       <c r="L35" t="n">
         <v>3.02</v>
@@ -2445,7 +2864,19 @@
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>67</v>
+        <v>68</v>
+      </c>
+      <c r="R35" s="3" t="n">
+        <v>44951</v>
+      </c>
+      <c r="S35" t="b">
+        <v>1</v>
+      </c>
+      <c r="T35" t="n">
+        <v>4</v>
+      </c>
+      <c r="U35" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="36">
@@ -2472,19 +2903,19 @@
         <v>5.53</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>45113</v>
+        <v>45114</v>
       </c>
       <c r="H36" t="n">
-        <v>527.7</v>
+        <v>517.05</v>
       </c>
       <c r="I36" t="n">
         <v>521.4623537770146</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="K36" t="n">
-        <v>6.19</v>
+        <v>4.04</v>
       </c>
       <c r="L36" t="n">
         <v>1.45</v>
@@ -2502,7 +2933,19 @@
         <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>50</v>
+        <v>51</v>
+      </c>
+      <c r="R36" s="3" t="n">
+        <v>45043</v>
+      </c>
+      <c r="S36" t="b">
+        <v>1</v>
+      </c>
+      <c r="T36" t="n">
+        <v>4</v>
+      </c>
+      <c r="U36" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="37">
@@ -2529,22 +2972,22 @@
         <v>7.81</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>45134</v>
+        <v>45135</v>
       </c>
       <c r="H37" t="n">
-        <v>554.05</v>
+        <v>574.35</v>
       </c>
       <c r="I37" t="n">
         <v>557.4375804466035</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K37" t="n">
-        <v>-7.16</v>
+        <v>-11.08</v>
       </c>
       <c r="L37" t="n">
-        <v>7.53</v>
+        <v>11.82</v>
       </c>
       <c r="M37" t="n">
         <v>0.75</v>
@@ -2559,7 +3002,19 @@
         <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R37" s="3" t="n">
+        <v>45134</v>
+      </c>
+      <c r="S37" t="b">
+        <v>1</v>
+      </c>
+      <c r="T37" t="n">
+        <v>2</v>
+      </c>
+      <c r="U37" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="38">
@@ -2586,28 +3041,28 @@
         <v>8.470000000000001</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>45203</v>
+        <v>45204</v>
       </c>
       <c r="H38" t="n">
-        <v>570.85</v>
+        <v>542.45</v>
       </c>
       <c r="I38" t="n">
         <v>557.1193006972887</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="K38" t="n">
-        <v>-0.61</v>
+        <v>-5.55</v>
       </c>
       <c r="L38" t="n">
-        <v>4.93</v>
+        <v>5.81</v>
       </c>
       <c r="M38" t="n">
-        <v>0.14</v>
+        <v>2.43</v>
       </c>
       <c r="N38" t="n">
-        <v>4.11</v>
+        <v>4.98</v>
       </c>
       <c r="O38" t="n">
         <v>3.66</v>
@@ -2616,7 +3071,19 @@
         <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>46</v>
+        <v>47</v>
+      </c>
+      <c r="R38" s="3" t="n">
+        <v>45169</v>
+      </c>
+      <c r="S38" t="b">
+        <v>1</v>
+      </c>
+      <c r="T38" t="n">
+        <v>3</v>
+      </c>
+      <c r="U38" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="39">
@@ -2643,19 +3110,19 @@
         <v>10.04</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>45278</v>
+        <v>45279</v>
       </c>
       <c r="H39" t="n">
-        <v>540.45</v>
+        <v>547.85</v>
       </c>
       <c r="I39" t="n">
         <v>544.1172065977778</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="K39" t="n">
-        <v>0.37</v>
+        <v>-1</v>
       </c>
       <c r="L39" t="n">
         <v>3.88</v>
@@ -2673,7 +3140,19 @@
         <v>1</v>
       </c>
       <c r="Q39" t="n">
-        <v>51</v>
+        <v>52</v>
+      </c>
+      <c r="R39" s="3" t="n">
+        <v>45225</v>
+      </c>
+      <c r="S39" t="b">
+        <v>1</v>
+      </c>
+      <c r="T39" t="n">
+        <v>3</v>
+      </c>
+      <c r="U39" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="40">
@@ -2700,25 +3179,25 @@
         <v>5.95</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>45316</v>
+        <v>45320</v>
       </c>
       <c r="H40" t="n">
-        <v>525.1</v>
+        <v>516.6</v>
       </c>
       <c r="I40" t="n">
         <v>517.5926804955784</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="K40" t="n">
-        <v>-4.15</v>
+        <v>-5.7</v>
       </c>
       <c r="L40" t="n">
-        <v>5.88</v>
+        <v>7.16</v>
       </c>
       <c r="M40" t="n">
-        <v>2.93</v>
+        <v>3.14</v>
       </c>
       <c r="N40" t="n">
         <v>4.08</v>
@@ -2730,7 +3209,19 @@
         <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="R40" s="3" t="n">
+        <v>45288</v>
+      </c>
+      <c r="S40" t="b">
+        <v>1</v>
+      </c>
+      <c r="T40" t="n">
+        <v>3</v>
+      </c>
+      <c r="U40" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="41">
@@ -2757,19 +3248,19 @@
         <v>6.56</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>45415</v>
+        <v>45418</v>
       </c>
       <c r="H41" t="n">
-        <v>516.9</v>
+        <v>530.3</v>
       </c>
       <c r="I41" t="n">
         <v>521.4803575889271</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="K41" t="n">
-        <v>-0.06</v>
+        <v>-2.65</v>
       </c>
       <c r="L41" t="n">
         <v>7.38</v>
@@ -2787,7 +3278,19 @@
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>65</v>
+        <v>66</v>
+      </c>
+      <c r="R41" s="3" t="n">
+        <v>45351</v>
+      </c>
+      <c r="S41" t="b">
+        <v>1</v>
+      </c>
+      <c r="T41" t="n">
+        <v>4</v>
+      </c>
+      <c r="U41" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="42">
@@ -2814,19 +3317,19 @@
         <v>6.53</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="H42" t="n">
-        <v>672.15</v>
+        <v>628.5</v>
       </c>
       <c r="I42" t="n">
         <v>631.7160521099644</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="K42" t="n">
-        <v>26.75</v>
+        <v>18.52</v>
       </c>
       <c r="L42" t="n">
         <v>2.27</v>
@@ -2835,7 +3338,7 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="N42" t="n">
-        <v>2.96</v>
+        <v>6.49</v>
       </c>
       <c r="O42" t="n">
         <v>2.59</v>
@@ -2844,7 +3347,19 @@
         <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>64</v>
+        <v>65</v>
+      </c>
+      <c r="R42" s="3" t="n">
+        <v>45442</v>
+      </c>
+      <c r="S42" t="b">
+        <v>1</v>
+      </c>
+      <c r="T42" t="n">
+        <v>4</v>
+      </c>
+      <c r="U42" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="43">
@@ -2871,22 +3386,22 @@
         <v>12.8</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>45548</v>
+        <v>45551</v>
       </c>
       <c r="H43" t="n">
-        <v>681.95</v>
+        <v>695.2</v>
       </c>
       <c r="I43" t="n">
         <v>687.9363311174071</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="K43" t="n">
-        <v>-8.5</v>
+        <v>-10.61</v>
       </c>
       <c r="L43" t="n">
-        <v>10.23</v>
+        <v>10.96</v>
       </c>
       <c r="M43" t="n">
         <v>0.78</v>
@@ -2901,7 +3416,19 @@
         <v>1</v>
       </c>
       <c r="Q43" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R43" s="3" t="n">
+        <v>45533</v>
+      </c>
+      <c r="S43" t="b">
+        <v>1</v>
+      </c>
+      <c r="T43" t="n">
+        <v>2</v>
+      </c>
+      <c r="U43" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="44">
@@ -2928,19 +3455,19 @@
         <v>7.94</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>45586</v>
+        <v>45587</v>
       </c>
       <c r="H44" t="n">
-        <v>661.95</v>
+        <v>657</v>
       </c>
       <c r="I44" t="n">
         <v>660.3216244276928</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="K44" t="n">
-        <v>-4.78</v>
+        <v>-5.49</v>
       </c>
       <c r="L44" t="n">
         <v>5.84</v>
@@ -2958,7 +3485,19 @@
         <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R44" s="3" t="n">
+        <v>45561</v>
+      </c>
+      <c r="S44" t="b">
+        <v>1</v>
+      </c>
+      <c r="T44" t="n">
+        <v>2</v>
+      </c>
+      <c r="U44" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="45">
@@ -2985,19 +3524,19 @@
         <v>8.08</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>45622</v>
+        <v>45623</v>
       </c>
       <c r="H45" t="n">
-        <v>628.35</v>
+        <v>649.9</v>
       </c>
       <c r="I45" t="n">
         <v>635.0666723072507</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="K45" t="n">
-        <v>4.36</v>
+        <v>1.08</v>
       </c>
       <c r="L45" t="n">
         <v>4.57</v>
@@ -3015,7 +3554,19 @@
         <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R45" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S45" t="b">
+        <v>1</v>
+      </c>
+      <c r="T45" t="n">
+        <v>2</v>
+      </c>
+      <c r="U45" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="46">
@@ -3042,19 +3593,19 @@
         <v>10.19</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>45698</v>
+        <v>45699</v>
       </c>
       <c r="H46" t="n">
-        <v>644.1</v>
+        <v>634.7</v>
       </c>
       <c r="I46" t="n">
         <v>634.9468877865963</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="K46" t="n">
-        <v>-0.89</v>
+        <v>-2.34</v>
       </c>
       <c r="L46" t="n">
         <v>7.59</v>
@@ -3072,7 +3623,19 @@
         <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>54</v>
+        <v>55</v>
+      </c>
+      <c r="R46" s="3" t="n">
+        <v>45624</v>
+      </c>
+      <c r="S46" t="b">
+        <v>1</v>
+      </c>
+      <c r="T46" t="n">
+        <v>4</v>
+      </c>
+      <c r="U46" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="47">
@@ -3099,19 +3662,19 @@
         <v>10.48</v>
       </c>
       <c r="G47" s="1" t="n">
-        <v>45741</v>
+        <v>45742</v>
       </c>
       <c r="H47" t="n">
-        <v>624.8</v>
+        <v>639.75</v>
       </c>
       <c r="I47" t="n">
         <v>635.9627921304188</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="K47" t="n">
-        <v>1.56</v>
+        <v>-0.8</v>
       </c>
       <c r="L47" t="n">
         <v>2.47</v>
@@ -3129,7 +3692,19 @@
         <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="R47" s="3" t="n">
+        <v>45715</v>
+      </c>
+      <c r="S47" t="b">
+        <v>1</v>
+      </c>
+      <c r="T47" t="n">
+        <v>2</v>
+      </c>
+      <c r="U47" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="48">
@@ -3156,19 +3731,19 @@
         <v>7.12</v>
       </c>
       <c r="G48" s="1" t="n">
-        <v>45862</v>
+        <v>45863</v>
       </c>
       <c r="H48" t="n">
-        <v>706.9</v>
+        <v>693.95</v>
       </c>
       <c r="I48" t="n">
         <v>697.3164234702131</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="K48" t="n">
-        <v>10.5</v>
+        <v>8.470000000000001</v>
       </c>
       <c r="L48" t="n">
         <v>1.98</v>
@@ -3186,7 +3761,19 @@
         <v>0</v>
       </c>
       <c r="Q48" t="n">
-        <v>82</v>
+        <v>83</v>
+      </c>
+      <c r="R48" s="3" t="n">
+        <v>45743</v>
+      </c>
+      <c r="S48" t="b">
+        <v>1</v>
+      </c>
+      <c r="T48" t="n">
+        <v>5</v>
+      </c>
+      <c r="U48" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="49">
@@ -3213,28 +3800,28 @@
         <v>6.67</v>
       </c>
       <c r="G49" s="1" t="n">
-        <v>45888</v>
+        <v>45889</v>
       </c>
       <c r="H49" t="n">
-        <v>727.95</v>
+        <v>751.85</v>
       </c>
       <c r="I49" t="n">
         <v>737.7949370702639</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="K49" t="n">
-        <v>-4.9</v>
+        <v>-8.34</v>
       </c>
       <c r="L49" t="n">
-        <v>5.89</v>
+        <v>8.57</v>
       </c>
       <c r="M49" t="n">
         <v>2.04</v>
       </c>
       <c r="N49" t="n">
-        <v>1.7</v>
+        <v>3.28</v>
       </c>
       <c r="O49" t="n">
         <v>-1.83</v>
@@ -3243,7 +3830,19 @@
         <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R49" s="3" t="n">
+        <v>45869</v>
+      </c>
+      <c r="S49" t="b">
+        <v>1</v>
+      </c>
+      <c r="T49" t="n">
+        <v>2</v>
+      </c>
+      <c r="U49" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="50">
@@ -3270,19 +3869,19 @@
         <v>9</v>
       </c>
       <c r="G50" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="H50" t="n">
-        <v>698.7</v>
+        <v>697.4</v>
       </c>
       <c r="I50" t="n">
         <v>697.6200200495036</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="K50" t="n">
-        <v>-7.07</v>
+        <v>-7.24</v>
       </c>
       <c r="L50" t="n">
         <v>8.19</v>
@@ -3300,7 +3899,19 @@
         <v>0</v>
       </c>
       <c r="Q50" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R50" s="3" t="n">
+        <v>45897</v>
+      </c>
+      <c r="S50" t="b">
+        <v>1</v>
+      </c>
+      <c r="T50" t="n">
+        <v>2</v>
+      </c>
+      <c r="U50" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="51">
@@ -3327,22 +3938,22 @@
         <v>5.3</v>
       </c>
       <c r="G51" s="1" t="n">
-        <v>45946</v>
+        <v>45947</v>
       </c>
       <c r="H51" t="n">
-        <v>725.7</v>
+        <v>735.15</v>
       </c>
       <c r="I51" t="n">
         <v>734.3322386613298</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K51" t="n">
-        <v>-4.06</v>
+        <v>-5.41</v>
       </c>
       <c r="L51" t="n">
-        <v>4.24</v>
+        <v>6.04</v>
       </c>
       <c r="M51" t="n">
         <v>0.57</v>
@@ -3357,7 +3968,19 @@
         <v>0</v>
       </c>
       <c r="Q51" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R51" s="3" t="n">
+        <v>45958</v>
+      </c>
+      <c r="S51" t="b">
+        <v>0</v>
+      </c>
+      <c r="T51" t="n">
+        <v>1</v>
+      </c>
+      <c r="U51" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="52">
@@ -3384,19 +4007,19 @@
         <v>5.1</v>
       </c>
       <c r="G52" s="1" t="n">
-        <v>45993</v>
+        <v>45994</v>
       </c>
       <c r="H52" t="n">
-        <v>717.35</v>
+        <v>710.65</v>
       </c>
       <c r="I52" t="n">
         <v>717.1810074743673</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="K52" t="n">
-        <v>-2.42</v>
+        <v>-3.33</v>
       </c>
       <c r="L52" t="n">
         <v>3.99</v>
@@ -3414,7 +4037,19 @@
         <v>0</v>
       </c>
       <c r="Q52" t="n">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="R52" s="3" t="n">
+        <v>45958</v>
+      </c>
+      <c r="S52" t="b">
+        <v>1</v>
+      </c>
+      <c r="T52" t="n">
+        <v>3</v>
+      </c>
+      <c r="U52" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="53">
@@ -3441,22 +4076,22 @@
         <v>5.83</v>
       </c>
       <c r="G53" s="1" t="n">
-        <v>46017</v>
+        <v>46020</v>
       </c>
       <c r="H53" t="n">
-        <v>743.3</v>
+        <v>753.1</v>
       </c>
       <c r="I53" t="n">
         <v>748.1153153718736</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="K53" t="n">
-        <v>-4.59</v>
+        <v>-5.97</v>
       </c>
       <c r="L53" t="n">
-        <v>5.62</v>
+        <v>6.24</v>
       </c>
       <c r="M53" t="n">
         <v>0.73</v>
@@ -3471,7 +4106,19 @@
         <v>0</v>
       </c>
       <c r="Q53" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R53" s="3" t="n">
+        <v>46021</v>
+      </c>
+      <c r="S53" t="b">
+        <v>0</v>
+      </c>
+      <c r="T53" t="n">
+        <v>1</v>
+      </c>
+      <c r="U53" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="54">
@@ -3498,19 +4145,19 @@
         <v>5.21</v>
       </c>
       <c r="G54" s="1" t="n">
-        <v>46050</v>
+        <v>46051</v>
       </c>
       <c r="H54" t="n">
-        <v>736.65</v>
+        <v>729.95</v>
       </c>
       <c r="I54" t="n">
         <v>735.4097083256988</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="K54" t="n">
-        <v>-2.18</v>
+        <v>-3.07</v>
       </c>
       <c r="L54" t="n">
         <v>4.22</v>
@@ -3528,7 +4175,19 @@
         <v>0</v>
       </c>
       <c r="Q54" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R54" s="3" t="n">
+        <v>46021</v>
+      </c>
+      <c r="S54" t="b">
+        <v>1</v>
+      </c>
+      <c r="T54" t="n">
+        <v>3</v>
+      </c>
+      <c r="U54" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="55">
@@ -3555,22 +4214,22 @@
         <v>6.1</v>
       </c>
       <c r="G55" s="1" t="n">
-        <v>46062</v>
+        <v>46063</v>
       </c>
       <c r="H55" t="n">
-        <v>754.85</v>
+        <v>764.85</v>
       </c>
       <c r="I55" t="n">
         <v>763.4917449860061</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K55" t="n">
-        <v>-3.41</v>
+        <v>-4.78</v>
       </c>
       <c r="L55" t="n">
-        <v>3.84</v>
+        <v>4.97</v>
       </c>
       <c r="M55" t="n">
         <v>1.74</v>
@@ -3585,7 +4244,19 @@
         <v>0</v>
       </c>
       <c r="Q55" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R55" s="3" t="n">
+        <v>46077</v>
+      </c>
+      <c r="S55" t="b">
+        <v>0</v>
+      </c>
+      <c r="T55" t="n">
+        <v>1</v>
+      </c>
+      <c r="U55" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="56">
@@ -3612,19 +4283,19 @@
         <v>6.85</v>
       </c>
       <c r="G56" s="1" t="n">
-        <v>46091</v>
+        <v>46092</v>
       </c>
       <c r="H56" t="n">
-        <v>789.9</v>
+        <v>761.6</v>
       </c>
       <c r="I56" t="n">
         <v>761.9556025303011</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="K56" t="n">
-        <v>3.28</v>
+        <v>-0.42</v>
       </c>
       <c r="L56" t="n">
         <v>2.02</v>
@@ -3633,7 +4304,7 @@
         <v>2.35</v>
       </c>
       <c r="N56" t="n">
-        <v>2.12</v>
+        <v>3.58</v>
       </c>
       <c r="O56" t="n">
         <v>1.32</v>
@@ -3642,7 +4313,19 @@
         <v>0</v>
       </c>
       <c r="Q56" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R56" s="3" t="n">
+        <v>46077</v>
+      </c>
+      <c r="S56" t="b">
+        <v>1</v>
+      </c>
+      <c r="T56" t="n">
+        <v>2</v>
+      </c>
+      <c r="U56" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="57">
@@ -3669,19 +4352,19 @@
         <v>8.619999999999999</v>
       </c>
       <c r="G57" s="1" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="H57" t="n">
-        <v>778.9</v>
+        <v>783.3</v>
       </c>
       <c r="I57" t="n">
         <v>782.8705895016685</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="K57" t="n">
-        <v>-2.27</v>
+        <v>-2.85</v>
       </c>
       <c r="L57" t="n">
         <v>4.11</v>
@@ -3699,7 +4382,19 @@
         <v>0</v>
       </c>
       <c r="Q57" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R57" s="3" t="n">
+        <v>46111</v>
+      </c>
+      <c r="S57" t="b">
+        <v>1</v>
+      </c>
+      <c r="T57" t="n">
+        <v>2</v>
+      </c>
+      <c r="U57" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="58">
@@ -3726,19 +4421,19 @@
         <v>7.13</v>
       </c>
       <c r="G58" s="1" t="n">
-        <v>46262</v>
+        <v>46265</v>
       </c>
       <c r="H58" t="n">
-        <v>829.65</v>
+        <v>820</v>
       </c>
       <c r="I58" t="n">
         <v>829.0940133989357</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="K58" t="n">
-        <v>5.92</v>
+        <v>4.69</v>
       </c>
       <c r="L58" t="n">
         <v>2.9</v>
@@ -3756,7 +4451,19 @@
         <v>0</v>
       </c>
       <c r="Q58" t="n">
-        <v>88</v>
+        <v>89</v>
+      </c>
+      <c r="R58" s="3" t="n">
+        <v>46140</v>
+      </c>
+      <c r="S58" t="b">
+        <v>1</v>
+      </c>
+      <c r="T58" t="n">
+        <v>6</v>
+      </c>
+      <c r="U58" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="59">
@@ -3807,6 +4514,14 @@
       <c r="Q59" t="n">
         <v>40</v>
       </c>
+      <c r="R59" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="S59" t="b">
+        <v>1</v>
+      </c>
+      <c r="T59" t="inlineStr"/>
+      <c r="U59" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -8765,7 +9480,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>72.90000000000001</v>
+        <v>74.5</v>
       </c>
     </row>
     <row r="6">
@@ -8775,7 +9490,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="7">
@@ -8785,7 +9500,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>310</v>
+        <v>313</v>
       </c>
     </row>
     <row r="8">
@@ -8795,7 +9510,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="9">
@@ -8805,7 +9520,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="10">
@@ -8815,7 +9530,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>150.2</v>
+        <v>151.2</v>
       </c>
     </row>
     <row r="11">
@@ -8825,7 +9540,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="12">
@@ -8835,7 +9550,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="13">
@@ -8845,7 +9560,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>22.8</v>
+        <v>21.1</v>
       </c>
     </row>
     <row r="14">
@@ -8855,7 +9570,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.65</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="15">
@@ -8865,7 +9580,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>5.88</v>
+        <v>3.23</v>
       </c>
     </row>
     <row r="16">
@@ -8875,7 +9590,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>-0.71</v>
+        <v>-2.99</v>
       </c>
     </row>
     <row r="17">
@@ -8885,7 +9600,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>35.79</v>
+        <v>32.95</v>
       </c>
     </row>
     <row r="18">
@@ -8895,7 +9610,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>43.9</v>
+        <v>31.6</v>
       </c>
     </row>
     <row r="19">
@@ -8905,7 +9620,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>5.01</v>
+        <v>5.68</v>
       </c>
     </row>
     <row r="20">
@@ -8915,7 +9630,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>4.46</v>
+        <v>5.01</v>
       </c>
     </row>
     <row r="21">
@@ -8935,7 +9650,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>20</v>
+        <v>29</v>
       </c>
     </row>
     <row r="23">
@@ -8945,7 +9660,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="24">
@@ -8955,7 +9670,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.81</v>
+        <v>1.86</v>
       </c>
     </row>
     <row r="25">
@@ -8975,7 +9690,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>3.32</v>
+        <v>3.73</v>
       </c>
     </row>
     <row r="27">
@@ -8995,7 +9710,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>15</v>
+        <v>21</v>
       </c>
     </row>
     <row r="29">
